--- a/data/Lead_information_Formulario_Brasil_Chrome.xlsx
+++ b/data/Lead_information_Formulario_Brasil_Chrome.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>URL</t>
   </si>
@@ -64,124 +64,34 @@
     <t>Dispositivo</t>
   </si>
   <si>
-    <t>https://www.chevrolet.com.br/gm-envolve</t>
-  </si>
-  <si>
-    <t>https://www.chevrolet.com.br/move-brasil-credito-taxistas-motoristas/tehno-interesse-spark</t>
-  </si>
-  <si>
-    <t>https://www.chevrolet.com.br/eletrico/captiva-ev</t>
-  </si>
-  <si>
-    <t>https://www.chevrolet.com.br/solicitar-contato</t>
-  </si>
-  <si>
-    <t>https://secure-developments.com/commonwealth/brasil/gm_forms/gm-envolve?model=envolve</t>
-  </si>
-  <si>
-    <t>https://secure-developments.com/commonwealth/brasil/gm_forms/move-spark</t>
-  </si>
-  <si>
-    <t>https://secure-developments.com/commonwealth/brasil/gm_forms/captiva-ev-2026?model=Captiva%20EV</t>
-  </si>
-  <si>
-    <t>https://secure-developments.com/commonwealth/brasil/gm_forms/raq</t>
-  </si>
-  <si>
-    <t>Carlos Marcelo</t>
-  </si>
-  <si>
-    <t>Diego Gabriel</t>
-  </si>
-  <si>
-    <t>Martín</t>
-  </si>
-  <si>
-    <t>Andrea Camila</t>
-  </si>
-  <si>
-    <t>Romero</t>
-  </si>
-  <si>
-    <t>Morales</t>
-  </si>
-  <si>
-    <t>Diaz Soto</t>
-  </si>
-  <si>
-    <t>Diaz</t>
-  </si>
-  <si>
-    <t>92942538643</t>
-  </si>
-  <si>
-    <t>10809087812</t>
-  </si>
-  <si>
-    <t>87129920890</t>
-  </si>
-  <si>
-    <t>00684300001</t>
-  </si>
-  <si>
-    <t>77346841000180</t>
-  </si>
-  <si>
-    <t>32114464000115</t>
-  </si>
-  <si>
-    <t>89734204000160</t>
-  </si>
-  <si>
-    <t>04091233000106</t>
-  </si>
-  <si>
-    <t>40240550</t>
-  </si>
-  <si>
-    <t>60531300</t>
-  </si>
-  <si>
-    <t>76824430</t>
-  </si>
-  <si>
-    <t>65636670</t>
-  </si>
-  <si>
-    <t>16913756962</t>
-  </si>
-  <si>
-    <t>90954040666</t>
-  </si>
-  <si>
-    <t>96945991301</t>
-  </si>
-  <si>
-    <t>29972777621</t>
-  </si>
-  <si>
-    <t>carlosmarceloromero_br48_chrome@mrm.com</t>
-  </si>
-  <si>
-    <t>diegogabrielmorales_br79_chrome@mrm.com</t>
-  </si>
-  <si>
-    <t>martindiazsoto_br45_chrome@mrm.com</t>
-  </si>
-  <si>
-    <t>andreacamiladiaz_br82_chrome@mrm.com</t>
-  </si>
-  <si>
-    <t>V425KJW2XR7U6AZSE</t>
-  </si>
-  <si>
-    <t>6JGB4U2073TZARXKV</t>
-  </si>
-  <si>
-    <t>VHAFZJZ73WY4L3YX9</t>
-  </si>
-  <si>
-    <t>MR2JD8U9928GW9C4Z</t>
+    <t>https://www.chevrolet.com.br/content/chevrolet/sa/br/pt/testing-folder/raq-eletricos-revamp.html</t>
+  </si>
+  <si>
+    <t>https://secure-developments.com/commonwealth/brasil/gm_forms/raq-eletricos-revamp</t>
+  </si>
+  <si>
+    <t>Rodrigo</t>
+  </si>
+  <si>
+    <t>Nuñez</t>
+  </si>
+  <si>
+    <t>26495567065</t>
+  </si>
+  <si>
+    <t>65983616000175</t>
+  </si>
+  <si>
+    <t>65042120</t>
+  </si>
+  <si>
+    <t>88930676265</t>
+  </si>
+  <si>
+    <t>rodrigonunez_br25_chrome@mrm.com</t>
+  </si>
+  <si>
+    <t>GW2MU1FM0XJA82W46</t>
   </si>
   <si>
     <t>chrome</t>
@@ -529,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -587,151 +497,40 @@
         <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" t="s">
-        <v>48</v>
-      </c>
       <c r="O2" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="P2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" t="s">
-        <v>49</v>
-      </c>
-      <c r="O3" t="s">
-        <v>53</v>
-      </c>
-      <c r="P3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
         <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" t="s">
-        <v>55</v>
-      </c>
-      <c r="P5" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1"/>
     <hyperlink ref="B2" r:id="rId2"/>
-    <hyperlink ref="A3" r:id="rId3"/>
-    <hyperlink ref="B3" r:id="rId4"/>
-    <hyperlink ref="A4" r:id="rId5"/>
-    <hyperlink ref="B4" r:id="rId6"/>
-    <hyperlink ref="A5" r:id="rId7"/>
-    <hyperlink ref="B5" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Lead_information_Formulario_Brasil_Chrome.xlsx
+++ b/data/Lead_information_Formulario_Brasil_Chrome.xlsx
@@ -64,34 +64,34 @@
     <t>Dispositivo</t>
   </si>
   <si>
-    <t>https://www.chevrolet.com.br/content/chevrolet/sa/br/pt/testing-folder/raq-eletricos-revamp.html</t>
-  </si>
-  <si>
-    <t>https://secure-developments.com/commonwealth/brasil/gm_forms/raq-eletricos-revamp</t>
-  </si>
-  <si>
-    <t>Rodrigo</t>
-  </si>
-  <si>
-    <t>Nuñez</t>
-  </si>
-  <si>
-    <t>26495567065</t>
-  </si>
-  <si>
-    <t>65983616000175</t>
-  </si>
-  <si>
-    <t>65042120</t>
-  </si>
-  <si>
-    <t>88930676265</t>
-  </si>
-  <si>
-    <t>rodrigonunez_br25_chrome@mrm.com</t>
-  </si>
-  <si>
-    <t>GW2MU1FM0XJA82W46</t>
+    <t>https://www.chevrolet.com.br/solicitar-contato</t>
+  </si>
+  <si>
+    <t>https://secure-developments.com/commonwealth/brasil/gm_forms/raq</t>
+  </si>
+  <si>
+    <t>Ramón</t>
+  </si>
+  <si>
+    <t>Quispe Soto</t>
+  </si>
+  <si>
+    <t>67355913999</t>
+  </si>
+  <si>
+    <t>82766347000104</t>
+  </si>
+  <si>
+    <t>69060118</t>
+  </si>
+  <si>
+    <t>36904207741</t>
+  </si>
+  <si>
+    <t>ramonquispesoto_br51_chrome@mrm.com</t>
+  </si>
+  <si>
+    <t>D0DM0BY48VTGVDG4P</t>
   </si>
   <si>
     <t>chrome</t>
